--- a/sample-data/Admin_lifecycle_2026-05.xlsx
+++ b/sample-data/Admin_lifecycle_2026-05.xlsx
@@ -427,13 +427,13 @@
         <v>Onboarding</v>
       </c>
       <c r="C2" t="str">
-        <v>2026-05-21</v>
+        <v>2026-04-20</v>
       </c>
       <c r="D2" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>ID card; email setup</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -447,7 +447,7 @@
         <v>Onboarding</v>
       </c>
       <c r="C3" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-09</v>
       </c>
       <c r="D3" t="str">
         <v>Y</v>
@@ -467,7 +467,7 @@
         <v>Onboarding</v>
       </c>
       <c r="C4" t="str">
-        <v>2026-04-04</v>
+        <v>2026-05-19</v>
       </c>
       <c r="D4" t="str">
         <v>Y</v>
@@ -487,7 +487,7 @@
         <v>Onboarding</v>
       </c>
       <c r="C5" t="str">
-        <v>2026-04-17</v>
+        <v>2026-05-25</v>
       </c>
       <c r="D5" t="str">
         <v>Y</v>
@@ -507,10 +507,10 @@
         <v>Onboarding</v>
       </c>
       <c r="C6" t="str">
-        <v>2026-05-21</v>
+        <v>2026-04-14</v>
       </c>
       <c r="D6" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -527,10 +527,10 @@
         <v>Onboarding</v>
       </c>
       <c r="C7" t="str">
-        <v>2026-05-09</v>
+        <v>2026-04-03</v>
       </c>
       <c r="D7" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -547,10 +547,10 @@
         <v>Onboarding</v>
       </c>
       <c r="C8" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-19</v>
       </c>
       <c r="D8" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -567,10 +567,10 @@
         <v>Onboarding</v>
       </c>
       <c r="C9" t="str">
-        <v>2026-04-22</v>
+        <v>2026-05-26</v>
       </c>
       <c r="D9" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -587,13 +587,13 @@
         <v>Onboarding</v>
       </c>
       <c r="C10" t="str">
-        <v>2026-04-11</v>
+        <v>2026-05-17</v>
       </c>
       <c r="D10" t="str">
         <v>Y</v>
       </c>
       <c r="E10" t="str">
-        <v>ID card; email setup</v>
+        <v/>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -607,7 +607,7 @@
         <v>Onboarding</v>
       </c>
       <c r="C11" t="str">
-        <v>2026-05-18</v>
+        <v>2026-04-16</v>
       </c>
       <c r="D11" t="str">
         <v>Y</v>
@@ -627,7 +627,7 @@
         <v>Onboarding</v>
       </c>
       <c r="C12" t="str">
-        <v>2026-04-04</v>
+        <v>2026-04-07</v>
       </c>
       <c r="D12" t="str">
         <v>Y</v>
@@ -647,10 +647,10 @@
         <v>Onboarding</v>
       </c>
       <c r="C13" t="str">
-        <v>2026-05-09</v>
+        <v>2026-04-16</v>
       </c>
       <c r="D13" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -667,16 +667,16 @@
         <v>Offboarding</v>
       </c>
       <c r="C14" t="str">
-        <v>2025-07-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="D14" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E14" t="str">
         <v>FnF pending</v>
       </c>
       <c r="F14" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
     </row>
     <row r="15">
@@ -687,7 +687,7 @@
         <v>Offboarding</v>
       </c>
       <c r="C15" t="str">
-        <v>2025-07-15</v>
+        <v>2026-05-11</v>
       </c>
       <c r="D15" t="str">
         <v>N</v>
@@ -707,16 +707,16 @@
         <v>Offboarding</v>
       </c>
       <c r="C16" t="str">
-        <v>2025-12-23</v>
+        <v>2026-05-19</v>
       </c>
       <c r="D16" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
     </row>
     <row r="17">
@@ -727,16 +727,16 @@
         <v>Offboarding</v>
       </c>
       <c r="C17" t="str">
-        <v>2025-12-22</v>
+        <v>2026-05-21</v>
       </c>
       <c r="D17" t="str">
         <v>Y</v>
       </c>
       <c r="E17" t="str">
-        <v/>
+        <v>FnF pending</v>
       </c>
       <c r="F17" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
     </row>
     <row r="18">
@@ -747,16 +747,16 @@
         <v>Offboarding</v>
       </c>
       <c r="C18" t="str">
-        <v>2025-11-21</v>
+        <v>2026-05-03</v>
       </c>
       <c r="D18" t="str">
         <v>Y</v>
       </c>
       <c r="E18" t="str">
-        <v/>
+        <v>FnF pending</v>
       </c>
       <c r="F18" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
     </row>
     <row r="19">
@@ -767,7 +767,7 @@
         <v>Offboarding</v>
       </c>
       <c r="C19" t="str">
-        <v>2025-11-26</v>
+        <v>2026-05-23</v>
       </c>
       <c r="D19" t="str">
         <v>Y</v>
@@ -787,13 +787,13 @@
         <v>Offboarding</v>
       </c>
       <c r="C20" t="str">
-        <v>2025-09-17</v>
+        <v>2026-05-21</v>
       </c>
       <c r="D20" t="str">
         <v>Y</v>
       </c>
       <c r="E20" t="str">
-        <v/>
+        <v>FnF pending</v>
       </c>
       <c r="F20" t="str">
         <v>Y</v>
@@ -807,16 +807,16 @@
         <v>Offboarding</v>
       </c>
       <c r="C21" t="str">
-        <v>2025-11-19</v>
+        <v>2026-05-17</v>
       </c>
       <c r="D21" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E21" t="str">
-        <v/>
+        <v>FnF pending</v>
       </c>
       <c r="F21" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
     </row>
     <row r="22">
@@ -827,16 +827,16 @@
         <v>Offboarding</v>
       </c>
       <c r="C22" t="str">
-        <v>2025-09-16</v>
+        <v>2026-05-26</v>
       </c>
       <c r="D22" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E22" t="str">
         <v>FnF pending</v>
       </c>
       <c r="F22" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
     </row>
     <row r="23">
@@ -847,13 +847,13 @@
         <v>Offboarding</v>
       </c>
       <c r="C23" t="str">
-        <v>2025-09-22</v>
+        <v>2026-05-13</v>
       </c>
       <c r="D23" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E23" t="str">
-        <v>FnF pending</v>
+        <v/>
       </c>
       <c r="F23" t="str">
         <v>N</v>
